--- a/artfynd/A 49813-2023 artfynd.xlsx
+++ b/artfynd/A 49813-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49813-2023 artfynd.xlsx
+++ b/artfynd/A 49813-2023 artfynd.xlsx
@@ -675,48 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104342629</v>
+        <v>104342622</v>
       </c>
       <c r="B2" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500329.0322328451</v>
+        <v>500329</v>
       </c>
       <c r="R2" t="n">
-        <v>6522524.532472338</v>
+        <v>6522525</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +750,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104342677</v>
+        <v>104342629</v>
       </c>
       <c r="B3" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500312.4398681939</v>
+        <v>500329</v>
       </c>
       <c r="R3" t="n">
-        <v>6522546.266992023</v>
+        <v>6522525</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,19 +857,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104342657</v>
+        <v>104342677</v>
       </c>
       <c r="B4" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,31 +898,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -967,13 +931,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500321.7670764312</v>
+        <v>500313</v>
       </c>
       <c r="R4" t="n">
-        <v>6522605.782089761</v>
+        <v>6522547</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,19 +964,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,46 +994,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104342622</v>
+        <v>104342657</v>
       </c>
       <c r="B5" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1087,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500329.0322328451</v>
+        <v>500322</v>
       </c>
       <c r="R5" t="n">
-        <v>6522524.532472338</v>
+        <v>6522606</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,19 +1070,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 49813-2023 artfynd.xlsx
+++ b/artfynd/A 49813-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342622</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342629</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342677</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,8 +1117,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104342657</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>